--- a/data/trans_orig/P33B_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R2-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100349</t>
+          <t>110037</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83857</t>
+          <t>91427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120222</t>
+          <t>132306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>156040</t>
+          <t>171817</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139438</t>
+          <t>152912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173594</t>
+          <t>190675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>256388</t>
+          <t>281854</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232940</t>
+          <t>253934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283121</t>
+          <t>309754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>534063</t>
+          <t>579591</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>514190</t>
+          <t>557322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>550555</t>
+          <t>598201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>518827</t>
+          <t>560366</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>501273</t>
+          <t>541508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>535429</t>
+          <t>579271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1052891</t>
+          <t>1139957</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1026158</t>
+          <t>1112057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1076339</t>
+          <t>1167877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>125727</t>
+          <t>139233</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>119441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169074</t>
+          <t>164063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>215997</t>
+          <t>237945</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193548</t>
+          <t>216987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236486</t>
+          <t>261651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>341724</t>
+          <t>377178</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232268</t>
+          <t>345644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>395301</t>
+          <t>408343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1067137</t>
+          <t>909684</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1023790</t>
+          <t>884854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1137115</t>
+          <t>929476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>742109</t>
+          <t>832893</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>721620</t>
+          <t>809187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>764558</t>
+          <t>853851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1809247</t>
+          <t>1742577</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1755670</t>
+          <t>1711412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1918703</t>
+          <t>1774111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>93123</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69502</t>
+          <t>77098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105983</t>
+          <t>114483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>137164</t>
+          <t>163353</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65185</t>
+          <t>143637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182338</t>
+          <t>184431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>221830</t>
+          <t>256476</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149333</t>
+          <t>227545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264741</t>
+          <t>287699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>620014</t>
+          <t>709950</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598697</t>
+          <t>688590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635178</t>
+          <t>725975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>796202</t>
+          <t>648906</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>751028</t>
+          <t>627828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>868181</t>
+          <t>668622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1416216</t>
+          <t>1358856</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373305</t>
+          <t>1327633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1488713</t>
+          <t>1387787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>143054</t>
+          <t>150328</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122533</t>
+          <t>130329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163837</t>
+          <t>171864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>238724</t>
+          <t>267159</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192544</t>
+          <t>241522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268307</t>
+          <t>293452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>381778</t>
+          <t>417487</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338570</t>
+          <t>385755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413701</t>
+          <t>450844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>783777</t>
+          <t>839734</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>762994</t>
+          <t>818198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>804298</t>
+          <t>859733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>851160</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>824286</t>
+          <t>824867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>900049</t>
+          <t>876797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1637646</t>
+          <t>1690894</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1605723</t>
+          <t>1657537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1680854</t>
+          <t>1722626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>354325</t>
+          <t>453359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>534440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>747925</t>
+          <t>840273</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>596729</t>
+          <t>796552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>819588</t>
+          <t>882039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1201720</t>
+          <t>1332994</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1064786</t>
+          <t>1274926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1300366</t>
+          <t>1392435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3004991</t>
+          <t>3038959</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2953708</t>
+          <t>2997240</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3104462</t>
+          <t>3078321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2911007</t>
+          <t>2893325</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2839344</t>
+          <t>2851559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3062203</t>
+          <t>2937046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5915999</t>
+          <t>5932285</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5817353</t>
+          <t>5872844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6052933</t>
+          <t>5990353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
